--- a/tp-calidad-sistema/Casos_de_Prueba_OrangeHRM.xlsx
+++ b/tp-calidad-sistema/Casos_de_Prueba_OrangeHRM.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="345" uniqueCount="104">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="437" uniqueCount="114">
   <si>
     <t>Caso</t>
   </si>
@@ -22,6 +22,9 @@
     <t>Resultado</t>
   </si>
   <si>
+    <t>Detalle del fallo</t>
+  </si>
+  <si>
     <t>Reintentos</t>
   </si>
   <si>
@@ -49,6 +52,9 @@
     <t>✗ FALLÓ</t>
   </si>
   <si>
+    <t>Error: expect(received).toBeGreaterThan(expected)</t>
+  </si>
+  <si>
     <t>Caso 3</t>
   </si>
   <si>
@@ -85,12 +91,18 @@
     <t>CP-075 El botón Reset limpia la búsqueda de Locations</t>
   </si>
   <si>
+    <t>Error: expect(received).toBe(expected) // Object.is equality</t>
+  </si>
+  <si>
     <t>Funcionalidad 3: Funcionalidad: Leave – Leave List</t>
   </si>
   <si>
     <t>CP-056 [SMOKE] La página Leave List carga correctamente</t>
   </si>
   <si>
+    <t>Error: expect.toBeVisible: Error: strict mode violation: locator('.oxd-table, .orangehrm-container') resolved to 2 elements:</t>
+  </si>
+  <si>
     <t>CP-057 La tabla de licencias tiene columnas visibles</t>
   </si>
   <si>
@@ -109,6 +121,9 @@
     <t>CP-061 [SMOKE] La página Leave Types carga correctamente</t>
   </si>
   <si>
+    <t>Error: Timed out 15000ms waiting for expect(locator).toBeVisible()</t>
+  </si>
+  <si>
     <t>CP-062 La tabla de Leave Types no está vacía</t>
   </si>
   <si>
@@ -121,12 +136,18 @@
     <t>CP-065 El formulario de nuevo Leave Type tiene campo Name</t>
   </si>
   <si>
+    <t>Error: locator.click: Timeout 15000ms exceeded.</t>
+  </si>
+  <si>
     <t>Funcionalidad 5: Funcionalidad: PIM – Emergency Contacts</t>
   </si>
   <si>
     <t>CP-036 [SMOKE] La pestaña Emergency Contacts carga correctamente</t>
   </si>
   <si>
+    <t>Error: expect.toBeVisible: Error: strict mode violation: locator('.oxd-table, .orangehrm-container') resolved to 4 elements:</t>
+  </si>
+  <si>
     <t>CP-037 El botón Add está visible en Emergency Contacts</t>
   </si>
   <si>
@@ -145,6 +166,9 @@
     <t>CP-041 [SMOKE] La pestaña Dependents carga correctamente</t>
   </si>
   <si>
+    <t>Error: expect.toBeVisible: Error: strict mode violation: locator('.orangehrm-container, .oxd-table') resolved to 4 elements:</t>
+  </si>
+  <si>
     <t>CP-042 El botón Add está visible en Dependents</t>
   </si>
   <si>
@@ -295,7 +319,13 @@
     <t>CP-017 [REGRESSION] La sección Supervisors tiene botón Add visible</t>
   </si>
   <si>
+    <t>Error: expect.toBeVisible: Error: strict mode violation: locator('.orangehrm-card-container').filter({ hasText: /supervisors/i }).first().getByRole('button', { name: 'Add' }) resolved to 3 elements:</t>
+  </si>
+  <si>
     <t>CP-018 [REGRESSION] Formulario de agregar supervisor muestra campos requeridos</t>
+  </si>
+  <si>
+    <t>Error: locator.click: Error: strict mode violation: locator('.orangehrm-card-container').filter({ hasText: /supervisors/i }).first().getByRole('button', { name: 'Add' }) resolved to 3 elements:</t>
   </si>
   <si>
     <t>CP-019 Cancel en formulario de supervisor no guarda cambios</t>
@@ -329,7 +359,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="7" x14ac:knownFonts="1">
+  <fonts count="8" x14ac:knownFonts="1">
     <font>
       <color theme="1"/>
       <family val="2"/>
@@ -354,6 +384,11 @@
     <font>
       <b/>
       <color rgb="FF9C0006"/>
+    </font>
+    <font>
+      <i/>
+      <color rgb="FF9C0006"/>
+      <sz val="9"/>
     </font>
     <font>
       <b/>
@@ -424,7 +459,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -447,19 +482,22 @@
     <xf numFmtId="0" fontId="4" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -801,16 +839,17 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:D108"/>
+  <dimension ref="A1:E108"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55" defaultColWidth="20"/>
   <cols>
     <col min="1" max="1" width="22" customWidth="1"/>
-    <col min="2" max="2" width="75" customWidth="1"/>
-    <col min="3" max="3" width="16" customWidth="1"/>
-    <col min="4" max="4" width="13" customWidth="1"/>
+    <col min="2" max="2" width="70" customWidth="1"/>
+    <col min="3" max="3" width="14" customWidth="1"/>
+    <col min="4" max="4" width="60" customWidth="1"/>
+    <col min="5" max="5" width="13" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="20" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="1" ht="20" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -823,1427 +862,1719 @@
       <c r="D1" s="1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="2" ht="18" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E1" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="2" ht="18" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B2" s="2"/>
       <c r="C2" s="2"/>
       <c r="D2" s="2"/>
-    </row>
-    <row r="3" ht="16" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E2" s="2"/>
+    </row>
+    <row r="3" ht="16" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C3" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="D3" s="5" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="4" ht="16" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
+        <v>8</v>
+      </c>
+      <c r="D3" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="E3" s="5" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="4" ht="30" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A4" s="6" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B4" s="6" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C4" s="7" t="s">
-        <v>11</v>
-      </c>
-      <c r="D4" s="8">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="5" ht="16" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
+        <v>12</v>
+      </c>
+      <c r="D4" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="E4" s="9">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" ht="16" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A5" s="3" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="D5" s="5" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="6" ht="16" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
+        <v>8</v>
+      </c>
+      <c r="D5" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="E5" s="5" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="6" ht="16" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A6" s="3" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="D6" s="5" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="7" ht="16" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
+        <v>8</v>
+      </c>
+      <c r="D6" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="E6" s="5" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="7" ht="16" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A7" s="3" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="D7" s="5" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="8" ht="6" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
+        <v>8</v>
+      </c>
+      <c r="D7" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="E7" s="5" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="8" ht="6" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B8" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C8" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D8" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="9" ht="18" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
+        <v>9</v>
+      </c>
+      <c r="E8" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="9" ht="18" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A9" s="2" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="B9" s="2"/>
       <c r="C9" s="2"/>
       <c r="D9" s="2"/>
-    </row>
-    <row r="10" ht="16" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E9" s="2"/>
+    </row>
+    <row r="10" ht="16" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A10" s="3" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="C10" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="D10" s="5" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="11" ht="16" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
+        <v>8</v>
+      </c>
+      <c r="D10" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="E10" s="5" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="11" ht="30" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A11" s="6" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B11" s="6" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="C11" s="7" t="s">
-        <v>11</v>
-      </c>
-      <c r="D11" s="8">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="12" ht="16" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
+        <v>12</v>
+      </c>
+      <c r="D11" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="E11" s="9">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="12" ht="16" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A12" s="3" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="C12" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="D12" s="5" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="13" ht="16" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
+        <v>8</v>
+      </c>
+      <c r="D12" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="E12" s="5" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="13" ht="16" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A13" s="3" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="C13" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="D13" s="5" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="14" ht="16" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
+        <v>8</v>
+      </c>
+      <c r="D13" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="E13" s="5" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="14" ht="30" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A14" s="6" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="B14" s="6" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="C14" s="7" t="s">
-        <v>11</v>
-      </c>
-      <c r="D14" s="8">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="15" ht="6" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
+        <v>12</v>
+      </c>
+      <c r="D14" s="8" t="s">
+        <v>26</v>
+      </c>
+      <c r="E14" s="9">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="15" ht="6" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B15" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C15" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D15" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="16" ht="18" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
+        <v>9</v>
+      </c>
+      <c r="E15" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="16" ht="18" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A16" s="2" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="B16" s="2"/>
       <c r="C16" s="2"/>
       <c r="D16" s="2"/>
-    </row>
-    <row r="17" ht="16" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E16" s="2"/>
+    </row>
+    <row r="17" ht="30" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A17" s="6" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B17" s="6" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="C17" s="7" t="s">
-        <v>11</v>
-      </c>
-      <c r="D17" s="8">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="18" ht="16" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
+        <v>12</v>
+      </c>
+      <c r="D17" s="8" t="s">
+        <v>29</v>
+      </c>
+      <c r="E17" s="9">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="18" ht="16" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A18" s="3" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="C18" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="D18" s="5" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="19" ht="16" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
+        <v>8</v>
+      </c>
+      <c r="D18" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="E18" s="5" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="19" ht="16" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A19" s="3" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="C19" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="D19" s="5" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="20" ht="16" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
+        <v>8</v>
+      </c>
+      <c r="D19" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="E19" s="5" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="20" ht="30" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A20" s="6" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="B20" s="6" t="s">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="C20" s="7" t="s">
-        <v>11</v>
-      </c>
-      <c r="D20" s="8">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="21" ht="16" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
+        <v>12</v>
+      </c>
+      <c r="D20" s="8" t="s">
+        <v>29</v>
+      </c>
+      <c r="E20" s="9">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="21" ht="16" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A21" s="3" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="B21" s="3" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="C21" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="D21" s="5" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="22" ht="6" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
+        <v>8</v>
+      </c>
+      <c r="D21" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="E21" s="5" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="22" ht="6" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B22" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C22" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D22" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="23" ht="18" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
+        <v>9</v>
+      </c>
+      <c r="E22" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="23" ht="18" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A23" s="2" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="B23" s="2"/>
       <c r="C23" s="2"/>
       <c r="D23" s="2"/>
-    </row>
-    <row r="24" ht="16" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E23" s="2"/>
+    </row>
+    <row r="24" ht="30" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A24" s="6" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B24" s="6" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="C24" s="7" t="s">
-        <v>11</v>
-      </c>
-      <c r="D24" s="8">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="25" ht="16" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
+        <v>12</v>
+      </c>
+      <c r="D24" s="8" t="s">
+        <v>36</v>
+      </c>
+      <c r="E24" s="9">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="25" ht="30" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A25" s="6" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B25" s="6" t="s">
-        <v>32</v>
+        <v>37</v>
       </c>
       <c r="C25" s="7" t="s">
-        <v>11</v>
-      </c>
-      <c r="D25" s="8">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="26" ht="16" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
+        <v>12</v>
+      </c>
+      <c r="D25" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="E25" s="9">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="26" ht="30" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A26" s="6" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="B26" s="6" t="s">
-        <v>33</v>
+        <v>38</v>
       </c>
       <c r="C26" s="7" t="s">
-        <v>11</v>
-      </c>
-      <c r="D26" s="8">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="27" ht="16" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
+        <v>12</v>
+      </c>
+      <c r="D26" s="8" t="s">
+        <v>36</v>
+      </c>
+      <c r="E26" s="9">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="27" ht="30" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A27" s="6" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="B27" s="6" t="s">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="C27" s="7" t="s">
-        <v>11</v>
-      </c>
-      <c r="D27" s="8">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="28" ht="16" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
+        <v>12</v>
+      </c>
+      <c r="D27" s="8" t="s">
+        <v>36</v>
+      </c>
+      <c r="E27" s="9">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="28" ht="30" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A28" s="6" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="B28" s="6" t="s">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="C28" s="7" t="s">
-        <v>11</v>
-      </c>
-      <c r="D28" s="8">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="29" ht="6" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
+        <v>12</v>
+      </c>
+      <c r="D28" s="8" t="s">
+        <v>41</v>
+      </c>
+      <c r="E28" s="9">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="29" ht="6" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B29" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C29" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D29" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="30" ht="18" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
+        <v>9</v>
+      </c>
+      <c r="E29" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="30" ht="18" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A30" s="2" t="s">
-        <v>36</v>
+        <v>42</v>
       </c>
       <c r="B30" s="2"/>
       <c r="C30" s="2"/>
       <c r="D30" s="2"/>
-    </row>
-    <row r="31" ht="16" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E30" s="2"/>
+    </row>
+    <row r="31" ht="30" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A31" s="6" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B31" s="6" t="s">
-        <v>37</v>
+        <v>43</v>
       </c>
       <c r="C31" s="7" t="s">
-        <v>11</v>
-      </c>
-      <c r="D31" s="8">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="32" ht="16" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
+        <v>12</v>
+      </c>
+      <c r="D31" s="8" t="s">
+        <v>44</v>
+      </c>
+      <c r="E31" s="9">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="32" ht="30" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A32" s="6" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B32" s="6" t="s">
-        <v>38</v>
+        <v>45</v>
       </c>
       <c r="C32" s="7" t="s">
-        <v>11</v>
-      </c>
-      <c r="D32" s="8">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="33" ht="16" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
+        <v>12</v>
+      </c>
+      <c r="D32" s="8" t="s">
+        <v>36</v>
+      </c>
+      <c r="E32" s="9">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="33" ht="30" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A33" s="6" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="B33" s="6" t="s">
-        <v>39</v>
+        <v>46</v>
       </c>
       <c r="C33" s="7" t="s">
-        <v>11</v>
-      </c>
-      <c r="D33" s="8">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="34" ht="16" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
+        <v>12</v>
+      </c>
+      <c r="D33" s="8" t="s">
+        <v>41</v>
+      </c>
+      <c r="E33" s="9">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="34" ht="30" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A34" s="6" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="B34" s="6" t="s">
-        <v>40</v>
+        <v>47</v>
       </c>
       <c r="C34" s="7" t="s">
-        <v>11</v>
-      </c>
-      <c r="D34" s="8">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="35" ht="16" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
+        <v>12</v>
+      </c>
+      <c r="D34" s="8" t="s">
+        <v>41</v>
+      </c>
+      <c r="E34" s="9">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="35" ht="30" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A35" s="6" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="B35" s="6" t="s">
+        <v>48</v>
+      </c>
+      <c r="C35" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="D35" s="8" t="s">
         <v>41</v>
       </c>
-      <c r="C35" s="7" t="s">
-        <v>11</v>
-      </c>
-      <c r="D35" s="8">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="36" ht="6" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E35" s="9">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="36" ht="6" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B36" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C36" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D36" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="37" ht="18" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
+        <v>9</v>
+      </c>
+      <c r="E36" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="37" ht="18" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A37" s="2" t="s">
-        <v>42</v>
+        <v>49</v>
       </c>
       <c r="B37" s="2"/>
       <c r="C37" s="2"/>
       <c r="D37" s="2"/>
-    </row>
-    <row r="38" ht="16" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E37" s="2"/>
+    </row>
+    <row r="38" ht="30" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A38" s="6" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B38" s="6" t="s">
-        <v>43</v>
+        <v>50</v>
       </c>
       <c r="C38" s="7" t="s">
-        <v>11</v>
-      </c>
-      <c r="D38" s="8">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="39" ht="16" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
+        <v>12</v>
+      </c>
+      <c r="D38" s="8" t="s">
+        <v>51</v>
+      </c>
+      <c r="E38" s="9">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="39" ht="30" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A39" s="6" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B39" s="6" t="s">
-        <v>44</v>
+        <v>52</v>
       </c>
       <c r="C39" s="7" t="s">
-        <v>11</v>
-      </c>
-      <c r="D39" s="8">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="40" ht="16" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
+        <v>12</v>
+      </c>
+      <c r="D39" s="8" t="s">
+        <v>36</v>
+      </c>
+      <c r="E39" s="9">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="40" ht="30" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A40" s="6" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="B40" s="6" t="s">
-        <v>45</v>
+        <v>53</v>
       </c>
       <c r="C40" s="7" t="s">
-        <v>11</v>
-      </c>
-      <c r="D40" s="8">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="41" ht="16" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
+        <v>12</v>
+      </c>
+      <c r="D40" s="8" t="s">
+        <v>41</v>
+      </c>
+      <c r="E40" s="9">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="41" ht="30" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A41" s="6" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="B41" s="6" t="s">
-        <v>46</v>
+        <v>54</v>
       </c>
       <c r="C41" s="7" t="s">
-        <v>11</v>
-      </c>
-      <c r="D41" s="8">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="42" ht="16" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
+        <v>12</v>
+      </c>
+      <c r="D41" s="8" t="s">
+        <v>41</v>
+      </c>
+      <c r="E41" s="9">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="42" ht="30" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A42" s="6" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="B42" s="6" t="s">
-        <v>47</v>
+        <v>55</v>
       </c>
       <c r="C42" s="7" t="s">
-        <v>11</v>
-      </c>
-      <c r="D42" s="8">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="43" ht="6" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
+        <v>12</v>
+      </c>
+      <c r="D42" s="8" t="s">
+        <v>41</v>
+      </c>
+      <c r="E42" s="9">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="43" ht="6" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B43" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C43" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D43" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="44" ht="18" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
+        <v>9</v>
+      </c>
+      <c r="E43" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="44" ht="18" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A44" s="2" t="s">
-        <v>48</v>
+        <v>56</v>
       </c>
       <c r="B44" s="2"/>
       <c r="C44" s="2"/>
       <c r="D44" s="2"/>
-    </row>
-    <row r="45" ht="16" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E44" s="2"/>
+    </row>
+    <row r="45" ht="16" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A45" s="3" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B45" s="3" t="s">
-        <v>49</v>
+        <v>57</v>
       </c>
       <c r="C45" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="D45" s="5" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="46" ht="16" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
+        <v>8</v>
+      </c>
+      <c r="D45" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="E45" s="5" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="46" ht="16" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A46" s="3" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B46" s="3" t="s">
-        <v>50</v>
+        <v>58</v>
       </c>
       <c r="C46" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="D46" s="5" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="47" ht="16" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
+        <v>8</v>
+      </c>
+      <c r="D46" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="E46" s="5" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="47" ht="16" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A47" s="3" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="B47" s="3" t="s">
-        <v>51</v>
+        <v>59</v>
       </c>
       <c r="C47" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="D47" s="5" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="48" ht="16" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
+        <v>8</v>
+      </c>
+      <c r="D47" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="E47" s="5" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="48" ht="16" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A48" s="3" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="B48" s="3" t="s">
-        <v>52</v>
+        <v>60</v>
       </c>
       <c r="C48" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="D48" s="5" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="49" ht="16" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
+        <v>8</v>
+      </c>
+      <c r="D48" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="E48" s="5" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="49" ht="16" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A49" s="3" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="B49" s="3" t="s">
-        <v>53</v>
+        <v>61</v>
       </c>
       <c r="C49" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="D49" s="5" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="50" ht="6" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
+        <v>8</v>
+      </c>
+      <c r="D49" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="E49" s="5" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="50" ht="6" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B50" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C50" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D50" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="51" ht="18" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
+        <v>9</v>
+      </c>
+      <c r="E50" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="51" ht="18" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A51" s="2" t="s">
-        <v>54</v>
+        <v>62</v>
       </c>
       <c r="B51" s="2"/>
       <c r="C51" s="2"/>
       <c r="D51" s="2"/>
-    </row>
-    <row r="52" ht="16" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E51" s="2"/>
+    </row>
+    <row r="52" ht="30" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A52" s="6" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B52" s="6" t="s">
-        <v>55</v>
+        <v>63</v>
       </c>
       <c r="C52" s="7" t="s">
-        <v>11</v>
-      </c>
-      <c r="D52" s="8">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="53" ht="16" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
+        <v>12</v>
+      </c>
+      <c r="D52" s="8" t="s">
+        <v>51</v>
+      </c>
+      <c r="E52" s="9">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="53" ht="30" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A53" s="6" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B53" s="6" t="s">
-        <v>56</v>
+        <v>64</v>
       </c>
       <c r="C53" s="7" t="s">
-        <v>11</v>
-      </c>
-      <c r="D53" s="8">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="54" ht="16" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
+        <v>12</v>
+      </c>
+      <c r="D53" s="8" t="s">
+        <v>36</v>
+      </c>
+      <c r="E53" s="9">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="54" ht="30" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A54" s="6" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="B54" s="6" t="s">
-        <v>57</v>
+        <v>65</v>
       </c>
       <c r="C54" s="7" t="s">
-        <v>11</v>
-      </c>
-      <c r="D54" s="8">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="55" ht="16" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
+        <v>12</v>
+      </c>
+      <c r="D54" s="8" t="s">
+        <v>41</v>
+      </c>
+      <c r="E54" s="9">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="55" ht="30" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A55" s="6" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="B55" s="6" t="s">
-        <v>58</v>
+        <v>66</v>
       </c>
       <c r="C55" s="7" t="s">
-        <v>11</v>
-      </c>
-      <c r="D55" s="8">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="56" ht="16" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
+        <v>12</v>
+      </c>
+      <c r="D55" s="8" t="s">
+        <v>41</v>
+      </c>
+      <c r="E55" s="9">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="56" ht="30" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A56" s="6" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="B56" s="6" t="s">
-        <v>59</v>
+        <v>67</v>
       </c>
       <c r="C56" s="7" t="s">
-        <v>11</v>
-      </c>
-      <c r="D56" s="8">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="57" ht="6" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
+        <v>12</v>
+      </c>
+      <c r="D56" s="8" t="s">
+        <v>41</v>
+      </c>
+      <c r="E56" s="9">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="57" ht="6" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B57" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C57" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D57" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="58" ht="18" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
+        <v>9</v>
+      </c>
+      <c r="E57" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="58" ht="18" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A58" s="2" t="s">
-        <v>60</v>
+        <v>68</v>
       </c>
       <c r="B58" s="2"/>
       <c r="C58" s="2"/>
       <c r="D58" s="2"/>
-    </row>
-    <row r="59" ht="16" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E58" s="2"/>
+    </row>
+    <row r="59" ht="16" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A59" s="3" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B59" s="3" t="s">
-        <v>61</v>
+        <v>69</v>
       </c>
       <c r="C59" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="D59" s="5" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="60" ht="16" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
+        <v>8</v>
+      </c>
+      <c r="D59" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="E59" s="5" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="60" ht="16" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A60" s="3" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B60" s="3" t="s">
-        <v>62</v>
+        <v>70</v>
       </c>
       <c r="C60" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="D60" s="5" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="61" ht="16" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
+        <v>8</v>
+      </c>
+      <c r="D60" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="E60" s="5" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="61" ht="16" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A61" s="3" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="B61" s="3" t="s">
-        <v>63</v>
+        <v>71</v>
       </c>
       <c r="C61" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="D61" s="5" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="62" ht="16" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
+        <v>8</v>
+      </c>
+      <c r="D61" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="E61" s="5" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="62" ht="30" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A62" s="6" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="B62" s="6" t="s">
-        <v>64</v>
+        <v>72</v>
       </c>
       <c r="C62" s="7" t="s">
-        <v>11</v>
-      </c>
-      <c r="D62" s="8">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="63" ht="16" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
+        <v>12</v>
+      </c>
+      <c r="D62" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="E62" s="9">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="63" ht="16" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A63" s="3" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="B63" s="3" t="s">
-        <v>65</v>
+        <v>73</v>
       </c>
       <c r="C63" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="D63" s="5" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="64" ht="6" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
+        <v>8</v>
+      </c>
+      <c r="D63" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="E63" s="5" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="64" ht="6" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B64" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C64" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D64" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="65" ht="18" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
+        <v>9</v>
+      </c>
+      <c r="E64" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="65" ht="18" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A65" s="2" t="s">
-        <v>66</v>
+        <v>74</v>
       </c>
       <c r="B65" s="2"/>
       <c r="C65" s="2"/>
       <c r="D65" s="2"/>
-    </row>
-    <row r="66" ht="16" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E65" s="2"/>
+    </row>
+    <row r="66" ht="16" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A66" s="3" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B66" s="3" t="s">
-        <v>67</v>
+        <v>75</v>
       </c>
       <c r="C66" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="D66" s="5" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="67" ht="16" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
+        <v>8</v>
+      </c>
+      <c r="D66" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="E66" s="5" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="67" ht="16" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A67" s="3" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B67" s="3" t="s">
-        <v>68</v>
+        <v>76</v>
       </c>
       <c r="C67" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="D67" s="5" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="68" ht="16" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
+        <v>8</v>
+      </c>
+      <c r="D67" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="E67" s="5" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="68" ht="16" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A68" s="3" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="B68" s="3" t="s">
-        <v>69</v>
+        <v>77</v>
       </c>
       <c r="C68" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="D68" s="5" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="69" ht="16" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
+        <v>8</v>
+      </c>
+      <c r="D68" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="E68" s="5" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="69" ht="16" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A69" s="3" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="B69" s="3" t="s">
-        <v>70</v>
+        <v>78</v>
       </c>
       <c r="C69" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="D69" s="5" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="70" ht="16" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
+        <v>8</v>
+      </c>
+      <c r="D69" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="E69" s="5" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="70" ht="16" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A70" s="3" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="B70" s="3" t="s">
-        <v>71</v>
+        <v>79</v>
       </c>
       <c r="C70" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="D70" s="5" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="71" ht="6" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
+        <v>8</v>
+      </c>
+      <c r="D70" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="E70" s="5" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="71" ht="6" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B71" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C71" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D71" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="72" ht="18" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
+        <v>9</v>
+      </c>
+      <c r="E71" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="72" ht="18" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A72" s="2" t="s">
-        <v>72</v>
+        <v>80</v>
       </c>
       <c r="B72" s="2"/>
       <c r="C72" s="2"/>
       <c r="D72" s="2"/>
-    </row>
-    <row r="73" ht="16" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E72" s="2"/>
+    </row>
+    <row r="73" ht="16" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A73" s="3" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B73" s="3" t="s">
-        <v>73</v>
+        <v>81</v>
       </c>
       <c r="C73" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="D73" s="5" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="74" ht="16" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
+        <v>8</v>
+      </c>
+      <c r="D73" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="E73" s="5" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="74" ht="16" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A74" s="3" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B74" s="3" t="s">
-        <v>74</v>
+        <v>82</v>
       </c>
       <c r="C74" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="D74" s="5" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="75" ht="16" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
+        <v>8</v>
+      </c>
+      <c r="D74" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="E74" s="5" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="75" ht="16" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A75" s="3" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="B75" s="3" t="s">
-        <v>75</v>
+        <v>83</v>
       </c>
       <c r="C75" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="D75" s="5" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="76" ht="16" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
+        <v>8</v>
+      </c>
+      <c r="D75" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="E75" s="5" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="76" ht="30" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A76" s="6" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="B76" s="6" t="s">
-        <v>76</v>
+        <v>84</v>
       </c>
       <c r="C76" s="7" t="s">
-        <v>11</v>
-      </c>
-      <c r="D76" s="8">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="77" ht="16" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
+        <v>12</v>
+      </c>
+      <c r="D76" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="E76" s="9">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="77" ht="30" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A77" s="6" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="B77" s="6" t="s">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="C77" s="7" t="s">
-        <v>11</v>
-      </c>
-      <c r="D77" s="8">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="78" ht="6" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
+        <v>12</v>
+      </c>
+      <c r="D77" s="8" t="s">
+        <v>36</v>
+      </c>
+      <c r="E77" s="9">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="78" ht="6" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A78" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B78" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C78" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D78" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="79" ht="18" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
+        <v>9</v>
+      </c>
+      <c r="E78" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="79" ht="18" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A79" s="2" t="s">
-        <v>78</v>
+        <v>86</v>
       </c>
       <c r="B79" s="2"/>
       <c r="C79" s="2"/>
       <c r="D79" s="2"/>
-    </row>
-    <row r="80" ht="16" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E79" s="2"/>
+    </row>
+    <row r="80" ht="30" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A80" s="6" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B80" s="6" t="s">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="C80" s="7" t="s">
-        <v>11</v>
-      </c>
-      <c r="D80" s="8">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="81" ht="16" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
+        <v>12</v>
+      </c>
+      <c r="D80" s="8" t="s">
+        <v>36</v>
+      </c>
+      <c r="E80" s="9">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="81" ht="30" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A81" s="6" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B81" s="6" t="s">
-        <v>80</v>
+        <v>88</v>
       </c>
       <c r="C81" s="7" t="s">
-        <v>11</v>
-      </c>
-      <c r="D81" s="8">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="82" ht="16" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A82" s="9" t="s">
-        <v>12</v>
-      </c>
-      <c r="B82" s="9" t="s">
-        <v>81</v>
-      </c>
-      <c r="C82" s="10" t="s">
-        <v>82</v>
-      </c>
-      <c r="D82" s="11" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="83" ht="16" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
+        <v>12</v>
+      </c>
+      <c r="D81" s="8" t="s">
+        <v>41</v>
+      </c>
+      <c r="E81" s="9">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="82" ht="16" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A82" s="10" t="s">
+        <v>14</v>
+      </c>
+      <c r="B82" s="10" t="s">
+        <v>89</v>
+      </c>
+      <c r="C82" s="11" t="s">
+        <v>90</v>
+      </c>
+      <c r="D82" s="10" t="s">
+        <v>9</v>
+      </c>
+      <c r="E82" s="12" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="83" ht="16" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A83" s="3" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="B83" s="3" t="s">
-        <v>83</v>
+        <v>91</v>
       </c>
       <c r="C83" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="D83" s="5" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="84" ht="16" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
+        <v>8</v>
+      </c>
+      <c r="D83" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="E83" s="5" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="84" ht="16" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A84" s="3" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="B84" s="3" t="s">
-        <v>84</v>
+        <v>92</v>
       </c>
       <c r="C84" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="D84" s="5" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="85" ht="6" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
+        <v>8</v>
+      </c>
+      <c r="D84" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="E84" s="5" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="85" ht="6" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A85" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B85" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C85" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D85" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="86" ht="18" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
+        <v>9</v>
+      </c>
+      <c r="E85" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="86" ht="18" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A86" s="2" t="s">
-        <v>85</v>
+        <v>93</v>
       </c>
       <c r="B86" s="2"/>
       <c r="C86" s="2"/>
       <c r="D86" s="2"/>
-    </row>
-    <row r="87" ht="16" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E86" s="2"/>
+    </row>
+    <row r="87" ht="30" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A87" s="6" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B87" s="6" t="s">
-        <v>86</v>
+        <v>94</v>
       </c>
       <c r="C87" s="7" t="s">
-        <v>11</v>
-      </c>
-      <c r="D87" s="8">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="88" ht="16" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
+        <v>12</v>
+      </c>
+      <c r="D87" s="8" t="s">
+        <v>41</v>
+      </c>
+      <c r="E87" s="9">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="88" ht="30" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A88" s="6" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B88" s="6" t="s">
-        <v>87</v>
+        <v>95</v>
       </c>
       <c r="C88" s="7" t="s">
-        <v>11</v>
-      </c>
-      <c r="D88" s="8">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="89" ht="16" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
+        <v>12</v>
+      </c>
+      <c r="D88" s="8" t="s">
+        <v>41</v>
+      </c>
+      <c r="E88" s="9">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="89" ht="30" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A89" s="6" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="B89" s="6" t="s">
-        <v>88</v>
+        <v>96</v>
       </c>
       <c r="C89" s="7" t="s">
-        <v>11</v>
-      </c>
-      <c r="D89" s="8">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="90" ht="16" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
+        <v>12</v>
+      </c>
+      <c r="D89" s="8" t="s">
+        <v>41</v>
+      </c>
+      <c r="E89" s="9">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="90" ht="30" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A90" s="6" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="B90" s="6" t="s">
-        <v>89</v>
+        <v>97</v>
       </c>
       <c r="C90" s="7" t="s">
-        <v>11</v>
-      </c>
-      <c r="D90" s="8">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="91" ht="16" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
+        <v>12</v>
+      </c>
+      <c r="D90" s="8" t="s">
+        <v>41</v>
+      </c>
+      <c r="E90" s="9">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="91" ht="30" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A91" s="6" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="B91" s="6" t="s">
-        <v>90</v>
+        <v>98</v>
       </c>
       <c r="C91" s="7" t="s">
-        <v>11</v>
-      </c>
-      <c r="D91" s="8">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="92" ht="6" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
+        <v>12</v>
+      </c>
+      <c r="D91" s="8" t="s">
+        <v>41</v>
+      </c>
+      <c r="E91" s="9">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="92" ht="6" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A92" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B92" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C92" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D92" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="93" ht="18" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
+        <v>9</v>
+      </c>
+      <c r="E92" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="93" ht="18" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A93" s="2" t="s">
-        <v>91</v>
+        <v>99</v>
       </c>
       <c r="B93" s="2"/>
       <c r="C93" s="2"/>
       <c r="D93" s="2"/>
-    </row>
-    <row r="94" ht="16" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E93" s="2"/>
+    </row>
+    <row r="94" ht="16" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A94" s="3" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B94" s="3" t="s">
-        <v>92</v>
+        <v>100</v>
       </c>
       <c r="C94" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="D94" s="5" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="95" ht="16" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
+        <v>8</v>
+      </c>
+      <c r="D94" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="E94" s="5" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="95" ht="30" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A95" s="6" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B95" s="6" t="s">
-        <v>93</v>
+        <v>101</v>
       </c>
       <c r="C95" s="7" t="s">
-        <v>11</v>
-      </c>
-      <c r="D95" s="8">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="96" ht="16" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
+        <v>12</v>
+      </c>
+      <c r="D95" s="8" t="s">
+        <v>102</v>
+      </c>
+      <c r="E95" s="9">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="96" ht="30" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A96" s="6" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="B96" s="6" t="s">
-        <v>94</v>
+        <v>103</v>
       </c>
       <c r="C96" s="7" t="s">
-        <v>11</v>
-      </c>
-      <c r="D96" s="8">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="97" ht="16" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
+        <v>12</v>
+      </c>
+      <c r="D96" s="8" t="s">
+        <v>104</v>
+      </c>
+      <c r="E96" s="9">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="97" ht="30" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A97" s="6" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="B97" s="6" t="s">
-        <v>95</v>
+        <v>105</v>
       </c>
       <c r="C97" s="7" t="s">
-        <v>11</v>
-      </c>
-      <c r="D97" s="8">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="98" ht="16" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
+        <v>12</v>
+      </c>
+      <c r="D97" s="8" t="s">
+        <v>104</v>
+      </c>
+      <c r="E97" s="9">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="98" ht="16" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A98" s="3" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="B98" s="3" t="s">
-        <v>96</v>
+        <v>106</v>
       </c>
       <c r="C98" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="D98" s="5" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="99" ht="6" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
+        <v>8</v>
+      </c>
+      <c r="D98" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="E98" s="5" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="99" ht="6" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A99" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B99" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C99" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D99" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="100" ht="18" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
+        <v>9</v>
+      </c>
+      <c r="E99" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="100" ht="18" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A100" s="2" t="s">
-        <v>97</v>
+        <v>107</v>
       </c>
       <c r="B100" s="2"/>
       <c r="C100" s="2"/>
       <c r="D100" s="2"/>
-    </row>
-    <row r="101" ht="16" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E100" s="2"/>
+    </row>
+    <row r="101" ht="16" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A101" s="3" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B101" s="3" t="s">
-        <v>98</v>
+        <v>108</v>
       </c>
       <c r="C101" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="D101" s="5" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="102" ht="16" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
+        <v>8</v>
+      </c>
+      <c r="D101" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="E101" s="5" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="102" ht="16" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A102" s="3" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B102" s="3" t="s">
-        <v>99</v>
+        <v>109</v>
       </c>
       <c r="C102" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="D102" s="5" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="103" ht="16" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
+        <v>8</v>
+      </c>
+      <c r="D102" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="E102" s="5" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="103" ht="16" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A103" s="3" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="B103" s="3" t="s">
-        <v>100</v>
+        <v>110</v>
       </c>
       <c r="C103" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="D103" s="5" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="104" ht="16" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
+        <v>8</v>
+      </c>
+      <c r="D103" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="E103" s="5" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="104" ht="16" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A104" s="3" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="B104" s="3" t="s">
-        <v>101</v>
+        <v>111</v>
       </c>
       <c r="C104" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="D104" s="5" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="105" ht="16" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
+        <v>8</v>
+      </c>
+      <c r="D104" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="E104" s="5" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="105" ht="30" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A105" s="6" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="B105" s="6" t="s">
-        <v>102</v>
+        <v>112</v>
       </c>
       <c r="C105" s="7" t="s">
-        <v>11</v>
-      </c>
-      <c r="D105" s="8">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="106" ht="6" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
+        <v>12</v>
+      </c>
+      <c r="D105" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="E105" s="9">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="106" ht="6" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A106" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B106" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C106" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D106" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="107" spans="1:4" x14ac:dyDescent="0.25">
+        <v>9</v>
+      </c>
+      <c r="E106" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="107" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A107" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B107" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C107" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D107" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="108" ht="18" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A108" s="12" t="s">
-        <v>103</v>
-      </c>
-      <c r="B108" s="12"/>
-      <c r="C108" s="12"/>
-      <c r="D108" s="12"/>
+        <v>9</v>
+      </c>
+      <c r="E107" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="108" ht="18" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A108" s="13" t="s">
+        <v>113</v>
+      </c>
+      <c r="B108" s="13"/>
+      <c r="C108" s="13"/>
+      <c r="D108" s="13"/>
+      <c r="E108" s="13"/>
     </row>
   </sheetData>
   <mergeCells count="16">
-    <mergeCell ref="A2:D2"/>
-    <mergeCell ref="A9:D9"/>
-    <mergeCell ref="A16:D16"/>
-    <mergeCell ref="A23:D23"/>
-    <mergeCell ref="A30:D30"/>
-    <mergeCell ref="A37:D37"/>
-    <mergeCell ref="A44:D44"/>
-    <mergeCell ref="A51:D51"/>
-    <mergeCell ref="A58:D58"/>
-    <mergeCell ref="A65:D65"/>
-    <mergeCell ref="A72:D72"/>
-    <mergeCell ref="A79:D79"/>
-    <mergeCell ref="A86:D86"/>
-    <mergeCell ref="A93:D93"/>
-    <mergeCell ref="A100:D100"/>
-    <mergeCell ref="A108:D108"/>
+    <mergeCell ref="A2:E2"/>
+    <mergeCell ref="A9:E9"/>
+    <mergeCell ref="A16:E16"/>
+    <mergeCell ref="A23:E23"/>
+    <mergeCell ref="A30:E30"/>
+    <mergeCell ref="A37:E37"/>
+    <mergeCell ref="A44:E44"/>
+    <mergeCell ref="A51:E51"/>
+    <mergeCell ref="A58:E58"/>
+    <mergeCell ref="A65:E65"/>
+    <mergeCell ref="A72:E72"/>
+    <mergeCell ref="A79:E79"/>
+    <mergeCell ref="A86:E86"/>
+    <mergeCell ref="A93:E93"/>
+    <mergeCell ref="A100:E100"/>
+    <mergeCell ref="A108:E108"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
